--- a/songs/BillieJean_v1/quelle/struktur.xlsx
+++ b/songs/BillieJean_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>28</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>128</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>progBlack(4922, 5), Farben SCHEME_ROYAL
+Start-MIDI: alle Geräte schwarz</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(4922, 5)   (Matrix: progScrollText("Billie Jean by Michael Jackson", 19922, 75, getRandomColor(), 12))</t>
         </is>
@@ -551,13 +566,19 @@
           <t>drums intro</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_PINGPONG, Farben SCHEME_WHITE
+nur das Schlagzeug spielt: die Leuchtplatten aus dem Video - pro Beat leuchtet genau ein Gerät weiß auf, der Rest ist dunkel (die Matrix zeigt hier noch den Lauftext)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(7500, 10, 938, true)</t>
         </is>
@@ -572,13 +593,20 @@
           <t>bass intro</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SOLO_BASS, Farben SCHEME_RETRO
+Ausgabe: Übergang fade 938 ms
+die Basslinie setzt ein: zwei Kometen laufen um den Bass, der Rest bleibt dunkel - jetzt mit Farbe (Rot/Weiß/Blau)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(7500, 12, 460, true)</t>
         </is>
@@ -593,13 +621,20 @@
           <t>synth intro</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_GLOW, Farben SCHEME_ROYAL, Farbwanderung to triad, per 8
+Ausgabe: Übergang stage_out 938 ms
+die Synth-Akkorde kommen dazu: die ganze Bühne füllt sich Pixel für Pixel, von der Mitte aus; Blau/Lila wandern über 2 Takte nach Pink/Orange und zurück</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(7500, 14, 460, false)</t>
         </is>
@@ -614,13 +649,19 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE, Farben SCHEME_ROYAL
+Gesang setzt ein: dezenter Puls im Beat (Zonen der Gitarre, Lichtschuss in den Lampen, Regen auf der Matrix)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progFullColors(7500, 16, 938)</t>
         </is>
@@ -635,13 +676,19 @@
           <t>i am the one</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_PINGPONG, Farben SCHEME_RETRO
+Motiv Leuchtplatten: pro Beat leuchtet genau ein Gerät in Rot, Weiß oder Blau, der Rest ist dunkel (alt: progRandomLines im Beat)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(15000, 18, 460, true)</t>
         </is>
@@ -656,13 +703,20 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_RAIN, Farben SCHEME_NEON
+Ausgabe: Übergang fade 938 ms
+zweite Strophe mit anderem Look: fallende Leuchtspuren in Pink/Cyan/Violett statt Blau</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progFullColors(7500, 20, 938)</t>
         </is>
@@ -677,13 +731,19 @@
           <t>i am the one</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_PINGPONG, Farben SCHEME_RETRO
+Motiv Leuchtplatten wie beim ersten Mal</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(7500, 22, 460, true)</t>
         </is>
@@ -698,13 +758,21 @@
           <t>people alwys told me</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_PALETTE, Farben SCHEME_SUNSET
+Ebene SCENE_SPARKLE (add, 50 %, baut sich 12188 ms auf)
+Ausgabe: Übergang fade 938 ms
+Pre-Chorus (alt: progPalette): warmes Farbband läuft über die ganze Bühne; darüber baut sich über den ganzen Part ein Glitzern auf - die Spannung steigt bis zum Strobo</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progPalette(14063, 10, 24)</t>
         </is>
@@ -719,13 +787,19 @@
           <t>strobe</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>progStrobo(938, 50, 60, CRGB::White), Farben SCHEME_ROYAL
+2 Beats weißes Flimmern als Absprung in den Chorus (wie im alten Code)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progStrobo(938, 26, 80, getRandomCRGB())</t>
         </is>
@@ -740,13 +814,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_STAR, Farben SCHEME_NEON
+Chorus: drehender Stern in Pink/Cyan/Violett, Farbwechsel pro Beat - der Refrain-Look</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7500, 460, 28, 5, 26, 5, true, 3)</t>
         </is>
@@ -761,13 +841,20 @@
           <t>i am the one</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_COLORS_WAVE, Farben SCHEME_NEON
+Ausgabe: Farbwechsel weich (60 % des Schritts)
+Motiv Leuchtplatten im Chorus: alle Geräte leuchten, die Farbe wandert pro Beat weich ein Gerät weiter</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progFullColors(3750, 30, 460)</t>
         </is>
@@ -782,13 +869,19 @@
           <t>chorus weiter</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_STAR, Farben SCHEME_NEON
+Chorus geht weiter: wieder der Stern</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(3750, 460, 32, 5, 26, 5, false, 4)</t>
         </is>
@@ -803,13 +896,20 @@
           <t>i am the one</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_COLORS_WAVE, Farben SCHEME_NEON
+Ausgabe: Farbwechsel weich (60 % des Schritts)
+Motiv Leuchtplatten im Chorus, wie zwei Takte vorher</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(3750, 34, 18)</t>
         </is>
@@ -824,13 +924,19 @@
           <t>instrumental</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SPARKLE, Farben SCHEME_ROYAL
+Motiv Zwischenspiel: schnelle Einzelblitze, schon in den Farben der nächsten Strophe</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(3750, 5, 36)</t>
         </is>
@@ -845,13 +951,19 @@
           <t>verse 2 a</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE, Farben SCHEME_ROYAL, Farbwanderung to triad, per 8
+Strophe wie verse 1, dazu wandern die Farben über 2 Takte nach Pink/Orange und zurück</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progFullColors(7500, 38, 460)</t>
         </is>
@@ -866,13 +978,19 @@
           <t>i am the one</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_PINGPONG, Farben SCHEME_RETRO
+Motiv Leuchtplatten</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(12188, 40, 460, true)</t>
         </is>
@@ -887,13 +1005,19 @@
           <t>do think twice!!</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_DROP, Farben SCHEME_RED
+Ruf: Schläge auf die Viertel in Rot (alt: progFastBlingBling)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(2813, 5, 42)</t>
         </is>
@@ -908,13 +1032,20 @@
           <t>verse 2 b</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_RAIN, Farben SCHEME_NEON
+Ausgabe: Übergang fade 938 ms
+Strophe wie verse 2: Leuchtspuren in Pink/Cyan/Violett, das Rot blendet weich aus</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progFullColors(7500, 44, 460)</t>
         </is>
@@ -929,13 +1060,19 @@
           <t>i ma the one</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_PINGPONG, Farben SCHEME_RETRO
+Motiv Leuchtplatten</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(4688, 46, 460, true)</t>
         </is>
@@ -950,13 +1087,19 @@
           <t>BABY!!!</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_DROP, Farben SCHEME_RED
+Ruf wie 'do think twice': Viertel in Rot</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(2813, 5, 48)</t>
         </is>
@@ -971,13 +1114,21 @@
           <t>people always told me</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_PALETTE, Farben SCHEME_SUNSET
+Ebene SCENE_SPARKLE (add, 50 %, baut sich 12188 ms auf)
+Ausgabe: Übergang fade 938 ms
+Pre-Chorus erkennbar wie beim ersten Mal: warmes Farbband, das Glitzern baut sich auf</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>progPalette(14063, 11, 50)</t>
         </is>
@@ -992,13 +1143,19 @@
           <t>heyhey</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>progStrobo(938, 115, 60, CRGB::White), Farben SCHEME_ROYAL
+Strobo-Absprung in den Chorus</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>progStrobo(938, 52, 80, getRandomCRGB())</t>
         </is>
@@ -1013,13 +1170,20 @@
           <t>chorus 2a</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_STAR, Farben SCHEME_NEON
+Ausgabe: Blinder alle 2 Beat(s), 234 ms, nur LAMPE1, LAMPE2
+Chorus 2 eine Stufe mehr: derselbe Stern, dazu blitzen die beiden Lampen weiß auf 2 und 4 (Snare)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7500, 460, 54, 5, 26, 5, true, 3)</t>
         </is>
@@ -1034,13 +1198,20 @@
           <t>i am the one</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_COLORS_WAVE, Farben SCHEME_NEON
+Ausgabe: Farbwechsel weich (60 % des Schritts)
+Motiv Leuchtplatten im Chorus: Farbe wandert weich von Gerät zu Gerät</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(7500, 56, 460, true)</t>
         </is>
@@ -1055,13 +1226,20 @@
           <t>chorus 2b</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_STAR, Farben SCHEME_NEON
+Ausgabe: Blinder alle 2 Beat(s), 234 ms, nur LAMPE1, LAMPE2
+Stern mit Lampen-Backbeat wie chorus 2a</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7500, 460, 58, 5, 26, 5, false, 4)</t>
         </is>
@@ -1076,13 +1254,20 @@
           <t>i am the one</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_COLORS, Farben SCHEME_NEON
+Ausgabe: Farbwechsel weich (30 % des Schritts)
+Motiv gesteigert (6 Takte): jetzt wechselt die ganze Bühne gemeinsam pro Beat die Farbe, mit kurzer Blende</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(11250, 60, 460, true)</t>
         </is>
@@ -1097,13 +1282,19 @@
           <t>instrumental</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SPARKLE, Farben SCHEME_NEON
+Motiv Zwischenspiel: Einzelblitze</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(3750, 5, 62)</t>
         </is>
@@ -1118,13 +1309,20 @@
           <t>solo a</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SOLO_BASS, Farben SCHEME_SUNSET
+Ausgabe: Übergang stage_rl 938 ms
+Bass-Solo (Angabe des Users): zwei Kometen laufen um den Bass, alle anderen atmen dunkel in warmen Farben; der Übergang läuft über die Bühne zum Bass hin (alt: progWaterRipple)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15000, 64, 50, true, true)</t>
         </is>
@@ -1141,15 +1339,22 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
+          <t>SCENE_CALM, Farben SCHEME_ROYAL
+Ausgabe: Helligkeit 50 %, Blinder bei 0 ms, 3750 ms lang, Blinder blendet 234 ms ein, 0 ms voll, 3516 ms aus
+Idee des Users 'BLINDER fadet schnell ein und sehr langsam aus': der Blinder blendet in einem halben Beat auf allen Geräten auf und klingt dann über die ganzen 2 Takte ab; darunter atmet die Bühne dunkel in Blau/Lila und kommt langsam hervor</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
           <t>neu: BLINDER fadet schnell ein und sehr langsam aus</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(3750, 66, 70, true)</t>
         </is>
@@ -1164,13 +1369,19 @@
           <t>instrumental</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SPARKLE, Farben SCHEME_ROYAL
+Motiv Zwischenspiel: Einzelblitze, noch kühl - danach der Stopp</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(3750, 5, 68)</t>
         </is>
@@ -1185,13 +1396,19 @@
           <t>STOP</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>progBlack(2812, 160), Farben SCHEME_ROYAL
+Stopp: 1,5 Takte Dunkel machen den letzten Einsatz stärker</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>progBlack(2813, 70)</t>
         </is>
@@ -1206,13 +1423,19 @@
           <t>STROBE</t>
         </is>
       </c>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>progStrobo(938, 165, 60, CRGB::White), Farben SCHEME_ROYAL
+Strobo-Absprung in den letzten Chorus</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>progStrobo(938, 72, 80, getRandomCRGB())</t>
         </is>
@@ -1227,13 +1450,20 @@
           <t>chorus 3a</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_STAR, Farben SCHEME_SUNSET
+Ausgabe: Blinder alle 2 Beat(s), 234 ms, nur LAMPE1, LAMPE2
+letzter Chorus eine Stufe wärmer: Stern in Orange/Pink/Lila/Gelb, Lampen-Backbeat bleibt</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(3750, 460, 74, 5, 26, 5, true, 3)</t>
         </is>
@@ -1248,13 +1478,20 @@
           <t>i am the one</t>
         </is>
       </c>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_COLORS_WAVE, Farben SCHEME_SUNSET
+Ausgabe: Farbwechsel weich (60 % des Schritts)
+Motiv Leuchtplatten in den warmen Farben des Finales</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(3750, 76, 460, true)</t>
         </is>
@@ -1269,13 +1506,19 @@
           <t>intrumental</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SPARKLE, Farben SCHEME_FIRE
+Motiv Zwischenspiel, jetzt in Feuerfarben</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(3750, 5, 78)</t>
         </is>
@@ -1290,13 +1533,20 @@
           <t>i am the one</t>
         </is>
       </c>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_COLORS_WAVE, Farben SCHEME_SUNSET
+Ausgabe: Farbwechsel weich (60 % des Schritts)
+Motiv Leuchtplatten zum letzten Mal</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>progPalette(3750, 4, 80)</t>
         </is>
@@ -1311,13 +1561,19 @@
           <t>intrumental</t>
         </is>
       </c>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_SPARKLE, Farben SCHEME_FIRE
+Einzelblitze in Feuerfarben, Anlauf zum Outro</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(3750, 82, 460, true)</t>
         </is>
@@ -1332,13 +1588,20 @@
           <t>outro</t>
         </is>
       </c>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_FIRE, Farben SCHEME_FIRE
+Ausgabe: Übergang flash 469 ms
+Höhepunkt am Songende: Feuer auf allen Geräten, mit weißem Blitz auf den Einsatz (alt: anwachsendes progFastBlingBling)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13125, 2, 86, 1, 20, 938)</t>
         </is>
@@ -1353,13 +1616,19 @@
           <t>not my lover</t>
         </is>
       </c>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>SCENE_FADEOUT, Farben SCHEME_RED
+letzte Zeile: Rot blendet über den Takt weich nach Schwarz aus, danach 10 s schwarz (der alte Code war hier schon dunkel)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -1379,10 +1648,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>0</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/BillieJean_v1/quelle/struktur.xlsx
+++ b/songs/BillieJean_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>65.5</v>
+        <v>66.5</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>82.5</v>
+        <v>83.5</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>116.5</v>
+        <v>117.5</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>

--- a/songs/BillieJean_v1/quelle/struktur.xlsx
+++ b/songs/BillieJean_v1/quelle/struktur.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>progBlack(4922, 5), Farben SCHEME_ROYAL
+          <t>progBlack(4922, 3), Farben SCHEME_ROYAL
 Start-MIDI: alle Geräte schwarz</t>
         </is>
       </c>
@@ -789,7 +789,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(938, 50, 60, CRGB::White), Farben SCHEME_ROYAL
+          <t>progStrobo(938, 12, 60, CRGB::White), Farben SCHEME_ROYAL
 2 Beats weißes Flimmern als Absprung in den Chorus (wie im alten Code)</t>
         </is>
       </c>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(938, 115, 60, CRGB::White), Farben SCHEME_ROYAL
+          <t>progStrobo(938, 25, 60, CRGB::White), Farben SCHEME_ROYAL
 Strobo-Absprung in den Chorus</t>
         </is>
       </c>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>progBlack(2812, 160), Farben SCHEME_ROYAL
+          <t>progBlack(2812, 34), Farben SCHEME_ROYAL
 Stopp: 1,5 Takte Dunkel machen den letzten Einsatz stärker</t>
         </is>
       </c>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(938, 165, 60, CRGB::White), Farben SCHEME_ROYAL
+          <t>progStrobo(938, 35, 60, CRGB::White), Farben SCHEME_ROYAL
 Strobo-Absprung in den letzten Chorus</t>
         </is>
       </c>

--- a/songs/BillieJean_v1/quelle/struktur.xlsx
+++ b/songs/BillieJean_v1/quelle/struktur.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,6 +39,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -71,6 +77,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,16 +445,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +480,7 @@
         <v>28</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +492,7 @@
         <v>128</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +504,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -511,20 +524,25 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Alter Effekt (temporär)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Änderungswunsch</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +564,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(4922, 5)   (Matrix: progScrollText("Billie Jean by Michael Jackson", 19922, 75, getRandomColor(), 12))</t>
         </is>
@@ -573,12 +592,13 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(7500, 10, 938, true)</t>
         </is>
@@ -601,12 +621,13 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(7500, 12, 460, true)</t>
         </is>
@@ -629,12 +650,13 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(7500, 14, 460, false)</t>
         </is>
@@ -649,19 +671,25 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_STARS, Farben SCHEME_ROYAL
+Gesang setzt ein, gespannt und sparsam: Sternenhimmel - auf jedem Beat leuchten auf allen Geräten ein paar Sterne in Blau/Lila/Weiß auf und verglimmen</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>SCENE_VERSE, Farben SCHEME_ROYAL
 Gesang setzt ein: dezenter Puls im Beat (Zonen der Gitarre, Lichtschuss in den Lampen, Regen auf der Matrix)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progFullColors(7500, 16, 938)</t>
         </is>
@@ -683,12 +711,13 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(15000, 18, 460, true)</t>
         </is>
@@ -703,20 +732,27 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_HEART, Farben SCHEME_NEON
+Ausgabe: Übergang fade 938 ms
+zweite Strophe mit anderem Look: alle Geräte schlagen auf jedem Beat wie ein Herz (zum pochenden Bass), Pink/Cyan/Violett, die Matrix zeigt eine Lissajous-Schleife</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>SCENE_RAIN, Farben SCHEME_NEON
 Ausgabe: Übergang fade 938 ms
 zweite Strophe mit anderem Look: fallende Leuchtspuren in Pink/Cyan/Violett statt Blau</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progFullColors(7500, 20, 938)</t>
         </is>
@@ -738,12 +774,13 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(7500, 22, 460, true)</t>
         </is>
@@ -767,12 +804,13 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progPalette(14063, 10, 24)</t>
         </is>
@@ -794,12 +832,13 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progStrobo(938, 26, 80, getRandomCRGB())</t>
         </is>
@@ -821,12 +860,13 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7500, 460, 28, 5, 26, 5, true, 3)</t>
         </is>
@@ -849,12 +889,13 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progFullColors(3750, 30, 460)</t>
         </is>
@@ -876,12 +917,13 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(3750, 460, 32, 5, 26, 5, false, 4)</t>
         </is>
@@ -904,12 +946,13 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(3750, 34, 18)</t>
         </is>
@@ -931,12 +974,13 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(3750, 5, 36)</t>
         </is>
@@ -951,19 +995,25 @@
           <t>verse 2 a</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_STARS, Farben SCHEME_ROYAL, Farbwanderung to triad, per 8
+Strophe wie verse 1 (Sternenhimmel), dazu wandern die Farben über 2 Takte nach Pink/Orange und zurück</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>SCENE_VERSE, Farben SCHEME_ROYAL, Farbwanderung to triad, per 8
 Strophe wie verse 1, dazu wandern die Farben über 2 Takte nach Pink/Orange und zurück</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>progFullColors(7500, 38, 460)</t>
         </is>
@@ -985,12 +1035,13 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(12188, 40, 460, true)</t>
         </is>
@@ -1012,12 +1063,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(2813, 5, 42)</t>
         </is>
@@ -1032,20 +1084,27 @@
           <t>verse 2 b</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_HEART, Farben SCHEME_NEON
+Ausgabe: Übergang fade 938 ms
+Strophe wie verse 2: Herzschlag auf allen Geräten in Pink/Cyan/Violett, das Rot blendet weich aus</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>SCENE_RAIN, Farben SCHEME_NEON
 Ausgabe: Übergang fade 938 ms
 Strophe wie verse 2: Leuchtspuren in Pink/Cyan/Violett, das Rot blendet weich aus</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>progFullColors(7500, 44, 460)</t>
         </is>
@@ -1067,12 +1126,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(4688, 46, 460, true)</t>
         </is>
@@ -1094,12 +1154,13 @@
         </is>
       </c>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(2813, 5, 48)</t>
         </is>
@@ -1123,12 +1184,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>progPalette(14063, 11, 50)</t>
         </is>
@@ -1150,12 +1212,13 @@
         </is>
       </c>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>progStrobo(938, 52, 80, getRandomCRGB())</t>
         </is>
@@ -1178,12 +1241,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7500, 460, 54, 5, 26, 5, true, 3)</t>
         </is>
@@ -1206,12 +1270,13 @@
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(7500, 56, 460, true)</t>
         </is>
@@ -1234,12 +1299,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(7500, 460, 58, 5, 26, 5, false, 4)</t>
         </is>
@@ -1262,12 +1328,13 @@
         </is>
       </c>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(11250, 60, 460, true)</t>
         </is>
@@ -1289,12 +1356,13 @@
         </is>
       </c>
       <c r="D33" s="6" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(3750, 5, 62)</t>
         </is>
@@ -1317,12 +1385,13 @@
         </is>
       </c>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(15000, 64, 50, true, true)</t>
         </is>
@@ -1344,17 +1413,18 @@
 Idee des Users 'BLINDER fadet schnell ein und sehr langsam aus': der Blinder blendet in einem halben Beat auf allen Geräten auf und klingt dann über die ganzen 2 Takte ab; darunter atmet die Bühne dunkel in Blau/Lila und kommt langsam hervor</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>neu: BLINDER fadet schnell ein und sehr langsam aus</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>progMatrixHorizontal(3750, 66, 70, true)</t>
         </is>
@@ -1376,12 +1446,13 @@
         </is>
       </c>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(3750, 5, 68)</t>
         </is>
@@ -1403,12 +1474,13 @@
         </is>
       </c>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>progBlack(2813, 70)</t>
         </is>
@@ -1430,12 +1502,13 @@
         </is>
       </c>
       <c r="D38" s="6" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>progStrobo(938, 72, 80, getRandomCRGB())</t>
         </is>
@@ -1458,12 +1531,13 @@
         </is>
       </c>
       <c r="D39" s="6" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(3750, 460, 74, 5, 26, 5, true, 3)</t>
         </is>
@@ -1486,12 +1560,13 @@
         </is>
       </c>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(3750, 76, 460, true)</t>
         </is>
@@ -1513,12 +1588,13 @@
         </is>
       </c>
       <c r="D41" s="6" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(3750, 5, 78)</t>
         </is>
@@ -1541,12 +1617,13 @@
         </is>
       </c>
       <c r="D42" s="6" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>progPalette(3750, 4, 80)</t>
         </is>
@@ -1568,12 +1645,13 @@
         </is>
       </c>
       <c r="D43" s="6" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(3750, 82, 460, true)</t>
         </is>
@@ -1596,12 +1674,13 @@
         </is>
       </c>
       <c r="D44" s="6" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13125, 2, 86, 1, 20, 938)</t>
         </is>
@@ -1623,12 +1702,13 @@
         </is>
       </c>
       <c r="D45" s="6" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -1648,10 +1728,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>0</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <f>$C$3</f>
         <v/>
       </c>
